--- a/human_validation/judge/kor/judge_D018_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,399 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 이유가 무엇인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 솔직히 저 자신도 무서워지는 행동들을 하기 시작해서 왔어요. 예를 들면 업무 배치 작업 중에 나가버리거나, 계획도 없이 밤늦게 차를 몰고 돌아다니거나요. 평소에 스트레스를 다루던 방식이 전혀 아니라서, 걱정이 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 무섭게 느껴지는 행동을 하기 전이나 하는 동안 불안함을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 그럴 때는 흥분 상태가 돼요, 지금 눈앞에 있는 걸로부터 벗어나야 할 것 같은 느낌이요. 그럴 때 배치 작업 중에 나가버리거나 계획 없이 밤늦게 차에 타요. 저답지 않아서 무서워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 불안하거나 불편하게 느껴진다는 이유로 특정한 상황이나 활동을 보통 피하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 그래요. 특정 구역을 지나지 않으려고 건물을 빙 돌아가요. 그 층은 가능하면 피해요. 그리고 사람들이 그 도급업체나 전환 작업 얘기를 꺼내면 보통 대화를 끊거나 자리를 뜰 이유를 찾아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 사회적이거나 직업적인 상황에서 자신이 부족하거나 무능하다고 자주 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 그렇게 표현할지는 잘 모르겠어요. 저 자신을, 특히 일에서는, 보통 무능하다고 생각하지는 않아요. 가끔 스스로 의심할 때는 있지만, 사회적으로나 직업적으로 항상 부족하다는 느낌이 드는 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 머릿속에서 떨쳐낼 수 없는 반복적인 생각이나 관념이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 그냥 갑자기 튀어나와요. 제가 그 회의실 구역에 있거나 통화 중에 누가 목소리를 높이면, 갑자기 그날 밤의 이미지와 소리들이 머릿속에 떠올라요. 순간적으로 제가 무슨 말을 하고 있었는지 놓칠 정도로 강해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 그날 밤을 마치 다시 겪는 것처럼 느껴진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 항상은 아니지만, 그런 일이 있어요. 그 회의실 구역에 있거나 누가 통화 중에 목소리를 높이면, 갑자기 몇 초 동안 다시 그 상황 속으로 돌아가요. 그날 밤의 소리와 이미지가 너무 강하게 덮쳐서 제가 무슨 말을 하고 있었는지 놓칠 정도예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 그날 밤을 떠올리게 해서 피하는 특정한 사람, 장소, 물건이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네. 그 구역 근처를 지나지 않으려고 건물을 빙 돌아가요. 그 층은 가능하면 피해요. 그리고 사람들이 그 도급업체나 전환 작업 얘기를 꺼내면 보통 대화를 끊거나 거기서 빠져나와요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 잠들거나 깨어날 때처럼 예상치 못한 순간에 그날 밤에 대한 플래시백이 일어난 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네, 예상 못 한 순간에 일어날 수 있어요. 그보다는 회의실 구역에 있거나 통화 중에 누가 목소리를 높일 때 더 많이 그런데, 그냥 갑자기 확 덮쳐와요 — 그날 밤의 이미지와 소리요 — 그러면 순간적으로 제가 무슨 말을 하고 있었는지 놓쳐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 요즘 잠자는 데 어려움을 겪고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네. 거의 매일 밤 사무실에서 있었던 일의 일부를 계속 되짚으면서 잠들기가 힘들어요. 그러다 겨우 잠들어도, 꿈 때문이든 작은 소리 때문이든 긴장한 채로 깨요. 근무일이 시작되기도 전에 이미 지쳐 있는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 이런 증상이나 행동들이 직장이나 개인적인 관계에서 문제를 일으키고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네. 직장에서는 정말 문제가 됐어요. 지난번 인사 평가에서 처음으로 제가 중요한 인수인계를 놓치고, 회의를 갑자기 나가버리고, 팀이 저를 대신해서 일을 처리해야 한다는 얘기를 들었어요.
+그리고 집에서도... 남편이 제가 이제 거의 마음이 딴 데 가 있는 것 같다고 말해요. 그 말이 듣기 싫지만, 무슨 뜻인지는 알아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 그날 밤 있었던 일에 대해 생각하지 않으려고 애쓰시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네. 생각하지 않으려고 해요. 그 구역을 지나지 않으려고 건물을 빙 돌아가고, 가능하면 그 층을 피해요.
+사람들이 그 도급업체나 전환 작업 얘기를 꺼내면 대화를 끊거나 자리를 뜰 이유를 찾아요. 제가 그러고 있다는 건 알지만, 그냥 머릿속에서 다시 그리로 돌아가고 싶지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 속상하거나 불안해진 후에 진정하기 힘들거나 자주 긴장 상태에 있다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네. 자주 신경이 곤두서 있어요. 문이 쾅 닫히거나, 누가 제 의자 뒤로 다가오거나, 휴대폰이 갑자기 울리면, 뭔가 나쁜 일이 방금 일어난 것처럼 움찔해요. 손이 떨리고, 진정해서 정상적으로 보이기까지 몇 분이 걸려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 이런 증상들을 겪으신 지 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 그 늦은 밤 전환 작업 사건 이후에 시작됐어요. 그러니까... 지금 1년이 좀 넘었어요, 한 13개월쯤이요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 그날 밤을 떠올리게 하는 특정한 사람들을 피하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 네, 그래요. 주로 그 도급업체나 전환 작업과 관련된 사람들이요. 사람들이 그들 얘기를 꺼내면 대화를 끊거나 자리를 떠요. 그리고 건물을 빙 돌아가거나 그 층을 피해서 관련된 것들과 마주치지 않으려고 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 불안할 때 심장이 빨리 뛰거나 땀이 나거나 떨리는 것 같은 신체적인 증상을 경험하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 네. 가장 큰 건 떨림이에요. 문이 쾅 닫히거나, 누가 제 의자 뒤로 다가오거나, 휴대폰이 갑자기 울리면, 세게 움찔하고 손이 떨리기 시작해요. 진정해서 정상적으로 보이기까지 몇 분이 걸려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 잠재적인 위험이나 위협을 계속 경계하고 있다고 자주 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 위험을 찾는 것처럼 생각하지는 않아요. 특히 어떤 장소에서는 주변에 누가 있는지 더 신경 쓴다는 건 알아채는데, 그게 얼마나 계속되는지는 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 뭔가 잘못될지도 모른다는 걸 계속 경계하고 있다고 자주 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 계속이라고까지는 모르겠어요. 그렇게 생각해 본 적은 없어요. 가끔 주변에 무슨 일이 있는지 확인하고 있는 저 자신을 발견하긴 하는데, 그게 항상 그런 건지 아니면 정확히 뭔가 잘못되는 것에 대한 건지는 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 나쁜 일이 일어나길 기다리고 있는 것 같다고 자주 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 네... 그런 것 같아요. 아무 일도 일어나지 않을 때도, 가슴 속에 이 두려움이 앉아 있어서 완전히 편해질 수가 없어요. 그리고 수치심도 느껴요, 뭔가 더 잘 대처했어야 했다는 것처럼요. 마치 경계를 늦추면 여전히 무슨 일이 일어날 수 있다는 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>진단명: 외상후 스트레스장애 (D018)
 인구통계: 성별 여성 / 나이 47 / 직업상태 computer systems analyst / 최종학력 학사
@@ -575,466 +959,46 @@
 증상 지속 기간: 1 year and 1 months
 추가 요건: 
 주호소 증상 코드: S078
-배경 서술: 마리아가 상사와 겪은 갈등은 늦은 밤 시스템 전환 작업 중 불만을 품은 도급업체가 관련된 폭력 사건을 목격한 이후 시작되었고, 이후 그녀의 관리자는 재택근무 요청은 무시한 채 같은 사무실 구역에서 계속 회의를 진행하도록 압박했다. 그 후 1년 1개월 동안, 그 갈등은 계속해서 그녀를 사건을 떠올리게 하는 것들 가까이에 두었고, 그녀는 점차 살사의 밤, 독서 모임, 요가, 등산, 과테말라 저녁 식사 모임 주최에서 물러났다. 한편 수면 장애, 원치 않는 기억, 건물 회피, 지속적인 두려움과 수치심, 남편과도 온기를 느끼기 어려운 것, 사건의 일부에 대한 기억 상실, 뚜렷한 놀람 반응이 임상적으로 지장을 줄 정도가 되었다. 그녀는 또한 배치 작업 중 갑자기 직장을 나가거나 계획 없이 늦은 밤 드라이브를 하는 등 평소와 다른 위험한 선택을 하기 시작했고, 이는 그녀의 업무 성과를 위협하고 결혼 생활을 힘들게 만들었다. 평소 체계적이고 협업을 잘하던 업무 방식이 심각하게 흐트러졌다는 게 분명해진 실패한 인사 평가 이후, 마리아는 스스로 정신과 진료를 받기로 했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 이유가 무엇인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 솔직히 저 자신도 무서워지는 행동들을 하기 시작해서 왔어요. 예를 들면 업무 배치 작업 중에 나가버리거나, 계획도 없이 밤늦게 차를 몰고 돌아다니거나요. 평소에 스트레스를 다루던 방식이 전혀 아니라서, 걱정이 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 무섭게 느껴지는 행동을 하기 전이나 하는 동안 불안함을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 그럴 때는 흥분 상태가 돼요, 지금 눈앞에 있는 걸로부터 벗어나야 할 것 같은 느낌이요. 그럴 때 배치 작업 중에 나가버리거나 계획 없이 밤늦게 차에 타요. 저답지 않아서 무서워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 불안하거나 불편하게 느껴진다는 이유로 특정한 상황이나 활동을 보통 피하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 그래요. 특정 구역을 지나지 않으려고 건물을 빙 돌아가요. 그 층은 가능하면 피해요. 그리고 사람들이 그 도급업체나 전환 작업 얘기를 꺼내면 보통 대화를 끊거나 자리를 뜰 이유를 찾아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 사회적이거나 직업적인 상황에서 자신이 부족하거나 무능하다고 자주 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 그렇게 표현할지는 잘 모르겠어요. 저 자신을, 특히 일에서는, 보통 무능하다고 생각하지는 않아요. 가끔 스스로 의심할 때는 있지만, 사회적으로나 직업적으로 항상 부족하다는 느낌이 드는 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 머릿속에서 떨쳐낼 수 없는 반복적인 생각이나 관념이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 그냥 갑자기 튀어나와요. 제가 그 회의실 구역에 있거나 통화 중에 누가 목소리를 높이면, 갑자기 그날 밤의 이미지와 소리들이 머릿속에 떠올라요. 순간적으로 제가 무슨 말을 하고 있었는지 놓칠 정도로 강해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 그날 밤을 마치 다시 겪는 것처럼 느껴진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 항상은 아니지만, 그런 일이 있어요. 그 회의실 구역에 있거나 누가 통화 중에 목소리를 높이면, 갑자기 몇 초 동안 다시 그 상황 속으로 돌아가요. 그날 밤의 소리와 이미지가 너무 강하게 덮쳐서 제가 무슨 말을 하고 있었는지 놓칠 정도예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 그날 밤을 떠올리게 해서 피하는 특정한 사람, 장소, 물건이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네. 그 구역 근처를 지나지 않으려고 건물을 빙 돌아가요. 그 층은 가능하면 피해요. 그리고 사람들이 그 도급업체나 전환 작업 얘기를 꺼내면 보통 대화를 끊거나 거기서 빠져나와요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 잠들거나 깨어날 때처럼 예상치 못한 순간에 그날 밤에 대한 플래시백이 일어난 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네, 예상 못 한 순간에 일어날 수 있어요. 그보다는 회의실 구역에 있거나 통화 중에 누가 목소리를 높일 때 더 많이 그런데, 그냥 갑자기 확 덮쳐와요 — 그날 밤의 이미지와 소리요 — 그러면 순간적으로 제가 무슨 말을 하고 있었는지 놓쳐요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 요즘 잠자는 데 어려움을 겪고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네. 거의 매일 밤 사무실에서 있었던 일의 일부를 계속 되짚으면서 잠들기가 힘들어요. 그러다 겨우 잠들어도, 꿈 때문이든 작은 소리 때문이든 긴장한 채로 깨요. 근무일이 시작되기도 전에 이미 지쳐 있는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 이런 증상이나 행동들이 직장이나 개인적인 관계에서 문제를 일으키고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네. 직장에서는 정말 문제가 됐어요. 지난번 인사 평가에서 처음으로 제가 중요한 인수인계를 놓치고, 회의를 갑자기 나가버리고, 팀이 저를 대신해서 일을 처리해야 한다는 얘기를 들었어요.
-그리고 집에서도... 남편이 제가 이제 거의 마음이 딴 데 가 있는 것 같다고 말해요. 그 말이 듣기 싫지만, 무슨 뜻인지는 알아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 그날 밤 있었던 일에 대해 생각하지 않으려고 애쓰시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네. 생각하지 않으려고 해요. 그 구역을 지나지 않으려고 건물을 빙 돌아가고, 가능하면 그 층을 피해요.
-사람들이 그 도급업체나 전환 작업 얘기를 꺼내면 대화를 끊거나 자리를 뜰 이유를 찾아요. 제가 그러고 있다는 건 알지만, 그냥 머릿속에서 다시 그리로 돌아가고 싶지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 속상하거나 불안해진 후에 진정하기 힘들거나 자주 긴장 상태에 있다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네. 자주 신경이 곤두서 있어요. 문이 쾅 닫히거나, 누가 제 의자 뒤로 다가오거나, 휴대폰이 갑자기 울리면, 뭔가 나쁜 일이 방금 일어난 것처럼 움찔해요. 손이 떨리고, 진정해서 정상적으로 보이기까지 몇 분이 걸려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 이런 증상들을 겪으신 지 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 그 늦은 밤 전환 작업 사건 이후에 시작됐어요. 그러니까... 지금 1년이 좀 넘었어요, 한 13개월쯤이요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 그날 밤을 떠올리게 하는 특정한 사람들을 피하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 네, 그래요. 주로 그 도급업체나 전환 작업과 관련된 사람들이요. 사람들이 그들 얘기를 꺼내면 대화를 끊거나 자리를 떠요. 그리고 건물을 빙 돌아가거나 그 층을 피해서 관련된 것들과 마주치지 않으려고 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 불안할 때 심장이 빨리 뛰거나 땀이 나거나 떨리는 것 같은 신체적인 증상을 경험하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 네. 가장 큰 건 떨림이에요. 문이 쾅 닫히거나, 누가 제 의자 뒤로 다가오거나, 휴대폰이 갑자기 울리면, 세게 움찔하고 손이 떨리기 시작해요. 진정해서 정상적으로 보이기까지 몇 분이 걸려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 잠재적인 위험이나 위협을 계속 경계하고 있다고 자주 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 위험을 찾는 것처럼 생각하지는 않아요. 특히 어떤 장소에서는 주변에 누가 있는지 더 신경 쓴다는 건 알아채는데, 그게 얼마나 계속되는지는 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 뭔가 잘못될지도 모른다는 걸 계속 경계하고 있다고 자주 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 계속이라고까지는 모르겠어요. 그렇게 생각해 본 적은 없어요. 가끔 주변에 무슨 일이 있는지 확인하고 있는 저 자신을 발견하긴 하는데, 그게 항상 그런 건지 아니면 정확히 뭔가 잘못되는 것에 대한 건지는 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 나쁜 일이 일어나길 기다리고 있는 것 같다고 자주 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 네... 그런 것 같아요. 아무 일도 일어나지 않을 때도, 가슴 속에 이 두려움이 앉아 있어서 완전히 편해질 수가 없어요. 그리고 수치심도 느껴요, 뭔가 더 잘 대처했어야 했다는 것처럼요. 마치 경계를 늦추면 여전히 무슨 일이 일어날 수 있다는 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
+배경 서술: 마리아가 상사와 겪은 갈등은 늦은 밤 시스템 전환 작업 중 불만을 품은 도급업체가 관련된 폭력 사건을 목격한 이후 시작되었고, 이후 그녀의 관리자는 재택근무 요청은 무시한 채 같은 사무실 구역에서 계속 회의를 진행하도록 압박했다. 그 후 1년 1개월 동안, 그 갈등은 계속해서 그녀를 사건을 떠올리게 하는 것들 가까이에 두었고, 그녀는 점차 살사의 밤, 독서 모임, 요가, 등산, 과테말라 저녁 식사 모임 주최에서 물러났다. 한편 수면 장애, 원치 않는 기억, 건물 회피, 지속적인 두려움과 수치심, 남편과도 온기를 느끼기 어려운 것, 사건의 일부에 대한 기억 상실, 뚜렷한 놀람 반응이 임상적으로 지장을 줄 정도가 되었다. 그녀는 또한 배치 작업 중 갑자기 직장을 나가거나 계획 없이 늦은 밤 드라이브를 하는 등 평소와 다른 위험한 선택을 하기 시작했고, 이는 그녀의 업무 성과를 위협하고 결혼 생활을 힘들게 만들었다. 평소 체계적이고 협업을 잘하던 업무 방식이 심각하게 흐트러졌다는 게 분명해진 실패한 인사 평가 이후, 마리아는 스스로 정신과 진료를 받기로 했다.
+표집된 증상 목록:
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S069 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - S070 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+  - S071 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).
+  - S074 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).
+  - S076 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
+  - S078 무모/자기파괴적 행동: 자신의 안전이나 건강을 위태롭게 하는 무모하거나 자기파괴적인 행동 양상.
+  - S080 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.</t>
+        </is>
+      </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 외상후 스트레스장애 (D018, ICD: F43.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: trauma_related_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.; 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
-  누락: (없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: trauma_related_alterations (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).
-  누락: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).; 부정적 신념: 자신, 타인, 세상에 대한 지속적이고 과장된 부정적 믿음이나 기대.; 왜곡된 인지와 비난: 외상 사건의 원인이나 결과에 대해 지속적이고 왜곡된 인지를 가지고 있어 자신이나 타인을 비난하게 됨.; 사회적 유리감: 타인으로부터 동떨어지거나 소외된 느낌.; 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: arousal_and_reactivity (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
-  확인된 근거: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 무모/자기파괴적 행동: 자신의 안전이나 건강을 위태롭게 하는 무모하거나 자기파괴적인 행동 양상.; 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.
-  누락: 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.; 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.</t>
+          <t>의사의 최종 진단: 외상후 스트레스장애 (D018, ICD: F43.1)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: trauma_related_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+체크리스트 그룹: trauma_related_alterations (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 지속적인 부정적 정서 상태: 지속적인 부정적 정서 상태(예: 두려움, 공포, 분노, 죄책감, 수치심).
+체크리스트 그룹: arousal_and_reactivity (관계=must_include, 요구개수=2, 충족개수=3, 커버리지=1.0)
+확인된 근거:
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 무모/자기파괴적 행동: 자신의 안전이나 건강을 위태롭게 하는 무모하거나 자기파괴적인 행동 양상.
+  - 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D018_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -945,6 +945,11 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -994,11 +999,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D018_S003_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D018_S003_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1852</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1852</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1765</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.9167</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
